--- a/t1_confection/Tech_Country_Matrix.xlsx
+++ b/t1_confection/Tech_Country_Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Desktop\CLG_repositories\OSTRAM\t1_confection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1BF395-9042-44F1-86FB-75CDE71146C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B55F54E-0D6C-40E8-B40C-05643901A0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrix" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="113">
+  <si>
+    <t>Enable Matrix Filtering:</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES = only pass technologies marked YES below  |  NO = pass ALL technologies from data</t>
+  </si>
   <si>
     <t>Tech \ Country</t>
   </si>
@@ -48,9 +57,6 @@
   </si>
   <si>
     <t>BCK</t>
-  </si>
-  <si>
-    <t>YES</t>
   </si>
   <si>
     <t>BIO</t>
@@ -363,13 +369,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -393,12 +410,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -446,25 +469,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -779,510 +806,521 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>10</v>
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>10</v>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>10</v>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>10</v>
+      <c r="B8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>10</v>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
+      <c r="B10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>8</v>
+      <c r="B11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>10</v>
+      <c r="B12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>10</v>
+      <c r="B13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="B14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
+      <c r="B15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>8</v>
+      <c r="B16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>10</v>
+      <c r="B18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>8</v>
+      <c r="B19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>10</v>
+      <c r="B20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>10</v>
+      <c r="B21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
+      <c r="B22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" errorTitle="Invalid Input" error="Please select YES or NO" sqref="B2:G22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" errorTitle="Invalid Input" error="Please select YES or NO" sqref="B1 B4:G24" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1294,47 +1332,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="A3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>32</v>
+      <c r="A5" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>33</v>
+      <c r="A7" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>35</v>
+      <c r="A8" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1362,371 +1403,371 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="A1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="A3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="B6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>43</v>
+      <c r="C7" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>43</v>
+      <c r="A9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>43</v>
+      <c r="A10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>43</v>
+      <c r="A11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>43</v>
+      <c r="A12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>43</v>
+      <c r="A13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>43</v>
+      <c r="A14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>43</v>
+      <c r="A15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>43</v>
+      <c r="A16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>43</v>
+      <c r="A17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>43</v>
+      <c r="A18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>43</v>
+      <c r="A19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>43</v>
+      <c r="A20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>43</v>
+      <c r="A21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>43</v>
+      <c r="A22" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="A23" s="9" t="s">
         <v>62</v>
       </c>
+      <c r="B23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>62</v>
+      <c r="C24" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>62</v>
+      <c r="A26" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>62</v>
+      <c r="A27" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>62</v>
+      <c r="A28" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>62</v>
+      <c r="A29" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>62</v>
+      <c r="A30" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>62</v>
+      <c r="A31" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>73</v>
       </c>
+      <c r="B32" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>73</v>
+      <c r="C33" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>73</v>
+      <c r="A35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>73</v>
+      <c r="A36" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1749,211 +1790,211 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>78</v>
+      <c r="A1" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>80</v>
+      <c r="A3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="7"/>
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="7"/>
+      <c r="A5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="7"/>
+      <c r="A6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="7"/>
+      <c r="A7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="7"/>
+      <c r="A8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="7"/>
+      <c r="A9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="7"/>
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="7"/>
+      <c r="A11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="7"/>
+      <c r="A12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="7"/>
+      <c r="A13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>92</v>
+      <c r="A14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="7"/>
+      <c r="A15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="7"/>
+      <c r="A16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="7"/>
+      <c r="A17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="7"/>
+      <c r="A18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="7"/>
+      <c r="A19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" s="7"/>
+      <c r="A20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="7"/>
+      <c r="A21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="7"/>
+      <c r="A22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="7"/>
+      <c r="A23" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="7"/>
+      <c r="A24" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1970,64 +2011,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>103</v>
+      <c r="A1" s="7" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>104</v>
+      <c r="A3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>105</v>
+      <c r="A4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>106</v>
+      <c r="A5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>107</v>
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>108</v>
+      <c r="A7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>109</v>
+      <c r="A8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>110</v>
+      <c r="A9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/t1_confection/Tech_Country_Matrix.xlsx
+++ b/t1_confection/Tech_Country_Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Desktop\CLG_repositories\OSTRAM\t1_confection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B55F54E-0D6C-40E8-B40C-05643901A0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44262385-7D8E-4504-87E3-7925CF622FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrix" sheetId="1" r:id="rId1"/>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -1359,7 +1359,7 @@
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
